--- a/task/关键标准答案.xlsx
+++ b/task/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R6eca6204acfe43c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R2fdf5ef47c854ff8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R0bd61ebcd49e444b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R4f9fd1233e3846cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Rbe704f7fe5134bdd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="Rb523db6f775f4ded"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R1ecbc3003feb4cde"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R88a93aa39d774371"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R290107f3bea84bfd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R8a103f595aa14551"/>
   </x:sheets>
 </x:workbook>
 </file>
